--- a/data/trans_orig/Q5409-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110316</t>
+          <t>110365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135047</t>
+          <t>134321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146327</t>
+          <t>146273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239037</t>
+          <t>238058</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254656</t>
+          <t>254381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35602</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125141</t>
+          <t>125078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138175</t>
+          <t>138854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149509</t>
+          <t>148754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169224</t>
+          <t>168691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282030</t>
+          <t>280283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304269</t>
+          <t>305115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -1645,82 +1645,82 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7615</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96872</t>
+          <t>96969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103584</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115916</t>
+          <t>116858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129870</t>
+          <t>130139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217491</t>
+          <t>217650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232129</t>
+          <t>231717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122987</t>
+          <t>123011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133169</t>
+          <t>133082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>177633</t>
+          <t>178259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>195811</t>
+          <t>195709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>304989</t>
+          <t>306301</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>325733</t>
+          <t>326553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>38076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85466</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>456411</t>
+          <t>458017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>477807</t>
+          <t>478159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>598254</t>
+          <t>599640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>628518</t>
+          <t>629432</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1064700</t>
+          <t>1063421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1101847</t>
+          <t>1100308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39076</t>
+          <t>37678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>125767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136465</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126548</t>
+          <t>127120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>147571</t>
+          <t>148139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257892</t>
+          <t>256911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281135</t>
+          <t>280668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123754</t>
+          <t>122993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142376</t>
+          <t>141794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143307</t>
+          <t>144995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166064</t>
+          <t>167022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272717</t>
+          <t>275025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302634</t>
+          <t>304118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>24259</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82472</t>
+          <t>82966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98365</t>
+          <t>98307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105662</t>
+          <t>105282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124366</t>
+          <t>124436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194978</t>
+          <t>195087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219367</t>
+          <t>219780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>30773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134794</t>
+          <t>134385</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153445</t>
+          <t>153407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>197360</t>
+          <t>197816</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>219037</t>
+          <t>220276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>341773</t>
+          <t>341970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>367624</t>
+          <t>369572</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34897</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>59091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58669</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91064</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>101166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142882</t>
+          <t>143888</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>486674</t>
+          <t>490906</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>519142</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>598070</t>
+          <t>599098</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>641223</t>
+          <t>639617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1098464</t>
+          <t>1098428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1150934</t>
+          <t>1149976</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23040</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>43204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115176</t>
+          <t>114482</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>135460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156752</t>
+          <t>156535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257852</t>
+          <t>257828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280313</t>
+          <t>281863</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22893</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141031</t>
+          <t>141247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155578</t>
+          <t>155225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185454</t>
+          <t>185283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205280</t>
+          <t>205251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332118</t>
+          <t>331189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355825</t>
+          <t>356106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92984</t>
+          <t>91890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107064</t>
+          <t>106850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110109</t>
+          <t>110445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128802</t>
+          <t>128610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208590</t>
+          <t>208899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232409</t>
+          <t>231844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164245</t>
+          <t>163824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172608</t>
+          <t>173086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185563</t>
+          <t>186384</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211948</t>
+          <t>213025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>352281</t>
+          <t>352951</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382252</t>
+          <t>382372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61041</t>
+          <t>59897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97567</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>97696</t>
+          <t>99251</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141697</t>
+          <t>142218</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>527256</t>
+          <t>527169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>553524</t>
+          <t>553188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>645385</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>685599</t>
+          <t>687376</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1180532</t>
+          <t>1180332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1228905</t>
+          <t>1231650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128626</t>
+          <t>128103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139226</t>
+          <t>138944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146541</t>
+          <t>146260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159575</t>
+          <t>158452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279243</t>
+          <t>278239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>294916</t>
+          <t>295139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137491</t>
+          <t>136867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149264</t>
+          <t>149097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179330</t>
+          <t>179349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193874</t>
+          <t>193015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321430</t>
+          <t>321133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339357</t>
+          <t>340248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>58819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112759</t>
+          <t>113005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125957</t>
+          <t>125721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>292006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352794</t>
+          <t>353305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>416273</t>
+          <t>417616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482455</t>
+          <t>482319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45054</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66230</t>
+          <t>66973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>174205</t>
+          <t>175089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188088</t>
+          <t>188728</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212763</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231896</t>
+          <t>232354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>393605</t>
+          <t>392274</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417059</t>
+          <t>415827</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68446</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>42090</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63173</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>56811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128915</t>
+          <t>126074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96123</t>
+          <t>101367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177023</t>
+          <t>177883</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>568147</t>
+          <t>566892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591915</t>
+          <t>592757</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>854242</t>
+          <t>857552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>955936</t>
+          <t>954106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1442072</t>
+          <t>1440919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1546959</t>
+          <t>1547649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Habitat-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99230</t>
+          <t>99378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110365</t>
+          <t>110483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134321</t>
+          <t>134652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146273</t>
+          <t>146309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>238058</t>
+          <t>237523</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254381</t>
+          <t>253648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36406</t>
+          <t>36906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125078</t>
+          <t>125937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138854</t>
+          <t>138986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148754</t>
+          <t>149043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168691</t>
+          <t>168966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280283</t>
+          <t>279975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305115</t>
+          <t>304248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103583</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116858</t>
+          <t>116722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130139</t>
+          <t>130331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217650</t>
+          <t>216858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231717</t>
+          <t>231924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123011</t>
+          <t>123012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133082</t>
+          <t>133073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>178259</t>
+          <t>177812</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>195709</t>
+          <t>195381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306301</t>
+          <t>306290</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>326553</t>
+          <t>326900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>456812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>478159</t>
+          <t>478663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>599640</t>
+          <t>597355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>629432</t>
+          <t>629313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1063421</t>
+          <t>1064970</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1100308</t>
+          <t>1102781</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37678</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125767</t>
+          <t>125511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136422</t>
+          <t>136433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127120</t>
+          <t>127822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148139</t>
+          <t>147137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256911</t>
+          <t>257638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280668</t>
+          <t>281576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27283</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>32656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122993</t>
+          <t>124145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141794</t>
+          <t>141937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144995</t>
+          <t>145311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167022</t>
+          <t>166191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275025</t>
+          <t>276242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304118</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82966</t>
+          <t>82801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98307</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105282</t>
+          <t>105806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124436</t>
+          <t>124852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195087</t>
+          <t>195495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219780</t>
+          <t>219269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>20322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>31115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22965</t>
+          <t>22929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47691</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134385</t>
+          <t>134305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153407</t>
+          <t>153238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>197816</t>
+          <t>198469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220276</t>
+          <t>220163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>341970</t>
+          <t>341833</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>369572</t>
+          <t>369334</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72854</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490906</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>518090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>599098</t>
+          <t>599549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>639617</t>
+          <t>642552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1098428</t>
+          <t>1102440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1149976</t>
+          <t>1153699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43204</t>
+          <t>44350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114482</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127908</t>
+          <t>127611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135460</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156535</t>
+          <t>156726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257828</t>
+          <t>258581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281863</t>
+          <t>281662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>22580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20869</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22995</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141247</t>
+          <t>140667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155225</t>
+          <t>155367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185283</t>
+          <t>184188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205251</t>
+          <t>205414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331189</t>
+          <t>331476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356106</t>
+          <t>355819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21639</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91890</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106850</t>
+          <t>106691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110445</t>
+          <t>109961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128610</t>
+          <t>128312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208899</t>
+          <t>207692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231844</t>
+          <t>232165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26616</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>39038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>45424</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163824</t>
+          <t>162650</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173086</t>
+          <t>172599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>186384</t>
+          <t>186097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213025</t>
+          <t>212639</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>352951</t>
+          <t>354012</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382372</t>
+          <t>381823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98575</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>527169</t>
+          <t>527034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>553188</t>
+          <t>553530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>642517</t>
+          <t>643084</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>687376</t>
+          <t>687257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1180332</t>
+          <t>1182439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1231650</t>
+          <t>1230158</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,22 +8412,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134593</t>
+          <t>149076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128103</t>
+          <t>142376</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138944</t>
+          <t>153694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,22 +8525,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153118</t>
+          <t>163059</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146260</t>
+          <t>155928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158452</t>
+          <t>169196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>287711</t>
+          <t>312135</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278239</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295139</t>
+          <t>320354</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,17 +8790,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28257</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>143919</t>
+          <t>160760</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136867</t>
+          <t>153258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149097</t>
+          <t>166210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>186867</t>
+          <t>206430</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179349</t>
+          <t>196869</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193015</t>
+          <t>213691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>330786</t>
+          <t>367189</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321133</t>
+          <t>357510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340248</t>
+          <t>376773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,67 +9211,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>6779</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>11835</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>6002</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>13020</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38024</t>
+          <t>44153</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>54952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>119702</t>
+          <t>139299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113005</t>
+          <t>131381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125721</t>
+          <t>146406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>332887</t>
+          <t>143855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292006</t>
+          <t>134919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353305</t>
+          <t>151072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>452589</t>
+          <t>283153</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>417616</t>
+          <t>271982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482319</t>
+          <t>293459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>21735</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>32899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46120</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>55093</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66973</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>182373</t>
+          <t>191028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>182969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188728</t>
+          <t>197415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222884</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212959</t>
+          <t>225047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232354</t>
+          <t>247324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>405257</t>
+          <t>428338</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>392274</t>
+          <t>414752</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>415827</t>
+          <t>441528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275073</t>
+          <t>294750</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275073</t>
+          <t>294750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275073</t>
+          <t>294750</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>509186</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>509186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>509186</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65131</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>97871</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56811</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>149991</t>
+          <t>165313</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101367</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177883</t>
+          <t>186255</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>580587</t>
+          <t>640162</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566892</t>
+          <t>625117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>592757</t>
+          <t>652826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>895756</t>
+          <t>750654</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>857552</t>
+          <t>730699</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>954106</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1476344</t>
+          <t>1390816</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1440919</t>
+          <t>1367443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1547649</t>
+          <t>1411539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
